--- a/news_daily/2026-10-15.xlsx
+++ b/news_daily/2026-10-15.xlsx
@@ -1105,13 +1105,17 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -1164,7 +1168,11 @@
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>2eb90392ccd0415aac49c1d6f19641ca</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>87667f3143bb8d52bb63b3d9</t>
@@ -1185,7 +1193,11 @@
       <c r="AL3" s="2" t="inlineStr"/>
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="2" t="inlineStr"/>
       <c r="AQ3" s="2" t="inlineStr"/>
       <c r="AR3" s="2" t="inlineStr"/>
@@ -1231,8 +1243,16 @@
       <c r="BH3" s="2" t="inlineStr"/>
       <c r="BI3" s="2" t="inlineStr"/>
       <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1477,13 +1497,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1536,7 +1560,11 @@
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>f2a598a100d74af89fd8cf7a2d59b23f</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>a8b8768d5e0ee24bfa2beebb</t>
@@ -1557,7 +1585,11 @@
       <c r="AL5" s="2" t="inlineStr"/>
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="2" t="inlineStr"/>
       <c r="AQ5" s="2" t="inlineStr"/>
       <c r="AR5" s="2" t="inlineStr"/>
@@ -1595,8 +1627,16 @@
       <c r="BH5" s="2" t="inlineStr"/>
       <c r="BI5" s="2" t="inlineStr"/>
       <c r="BJ5" s="2" t="inlineStr"/>
-      <c r="BK5" s="2" t="inlineStr"/>
-      <c r="BL5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -2020,28 +2060,32 @@
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2085,7 +2129,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -2094,7 +2138,11 @@
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr"/>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>27aa4f553fcb491d998dd8182541175b</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
           <t>cffa4df89d15861ee48b6771</t>
@@ -2115,7 +2163,11 @@
       <c r="AL8" s="2" t="inlineStr"/>
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr"/>
-      <c r="AO8" s="2" t="inlineStr"/>
+      <c r="AO8" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="2" t="inlineStr"/>
       <c r="AQ8" s="2" t="inlineStr"/>
       <c r="AR8" s="2" t="inlineStr"/>
@@ -2159,10 +2211,22 @@
         </is>
       </c>
       <c r="BH8" s="2" t="inlineStr"/>
-      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ8" s="2" t="inlineStr"/>
-      <c r="BK8" s="2" t="inlineStr"/>
-      <c r="BL8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2613,13 +2677,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2668,7 +2736,11 @@
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr"/>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>c5a1ce21435f453f8db7594a354bbe3a</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
           <t>2596027e6f0ec953e8279808</t>
@@ -2689,7 +2761,11 @@
       <c r="AL11" s="2" t="inlineStr"/>
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr"/>
-      <c r="AO11" s="2" t="inlineStr"/>
+      <c r="AO11" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="2" t="inlineStr"/>
       <c r="AQ11" s="2" t="inlineStr"/>
       <c r="AR11" s="2" t="inlineStr"/>
@@ -2735,8 +2811,16 @@
       <c r="BH11" s="2" t="inlineStr"/>
       <c r="BI11" s="2" t="inlineStr"/>
       <c r="BJ11" s="2" t="inlineStr"/>
-      <c r="BK11" s="2" t="inlineStr"/>
-      <c r="BL11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -3571,13 +3655,17 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3630,7 +3718,11 @@
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr"/>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>6e1200581437447c8f41a692b7ff922b</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
           <t>715c1cd85a48a94f342077b4</t>
@@ -3651,7 +3743,11 @@
       <c r="AL16" s="2" t="inlineStr"/>
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr"/>
-      <c r="AO16" s="2" t="inlineStr"/>
+      <c r="AO16" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP16" s="2" t="inlineStr"/>
       <c r="AQ16" s="2" t="inlineStr"/>
       <c r="AR16" s="2" t="inlineStr"/>
@@ -3689,8 +3785,16 @@
       <c r="BH16" s="2" t="inlineStr"/>
       <c r="BI16" s="2" t="inlineStr"/>
       <c r="BJ16" s="2" t="inlineStr"/>
-      <c r="BK16" s="2" t="inlineStr"/>
-      <c r="BL16" s="2" t="inlineStr"/>
+      <c r="BK16" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -4118,28 +4222,32 @@
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4183,7 +4291,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -4192,7 +4300,11 @@
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr"/>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>fc67efd3ddfa4456be0260b67048781f</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
           <t>735ea7097fde5fb16ae0da3d</t>
@@ -4213,7 +4325,11 @@
       <c r="AL19" s="2" t="inlineStr"/>
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr"/>
-      <c r="AO19" s="2" t="inlineStr"/>
+      <c r="AO19" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP19" s="2" t="inlineStr"/>
       <c r="AQ19" s="2" t="inlineStr"/>
       <c r="AR19" s="2" t="inlineStr"/>
@@ -4249,10 +4365,22 @@
         </is>
       </c>
       <c r="BH19" s="2" t="inlineStr"/>
-      <c r="BI19" s="2" t="inlineStr"/>
+      <c r="BI19" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ19" s="2" t="inlineStr"/>
-      <c r="BK19" s="2" t="inlineStr"/>
-      <c r="BL19" s="2" t="inlineStr"/>
+      <c r="BK19" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4688,28 +4816,32 @@
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -4753,7 +4885,7 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -4762,7 +4894,11 @@
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr"/>
-      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>d3c96de85a61433988c70669267a5ed2</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
           <t>48252fc83713df3d157d745d</t>
@@ -4783,7 +4919,11 @@
       <c r="AL22" s="2" t="inlineStr"/>
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr"/>
-      <c r="AO22" s="2" t="inlineStr"/>
+      <c r="AO22" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP22" s="2" t="inlineStr"/>
       <c r="AQ22" s="2" t="inlineStr"/>
       <c r="AR22" s="2" t="inlineStr"/>
@@ -4827,10 +4967,22 @@
         </is>
       </c>
       <c r="BH22" s="2" t="inlineStr"/>
-      <c r="BI22" s="2" t="inlineStr"/>
+      <c r="BI22" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ22" s="2" t="inlineStr"/>
-      <c r="BK22" s="2" t="inlineStr"/>
-      <c r="BL22" s="2" t="inlineStr"/>
+      <c r="BK22" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4881,13 +5033,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -4936,7 +5092,11 @@
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr"/>
-      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>778946b03aba4ef98cf96e79e17a53a7</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
           <t>b3aa3734526db3fad6bd60f6</t>
@@ -4957,7 +5117,11 @@
       <c r="AL23" s="2" t="inlineStr"/>
       <c r="AM23" s="2" t="inlineStr"/>
       <c r="AN23" s="2" t="inlineStr"/>
-      <c r="AO23" s="2" t="inlineStr"/>
+      <c r="AO23" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP23" s="2" t="inlineStr"/>
       <c r="AQ23" s="2" t="inlineStr"/>
       <c r="AR23" s="2" t="inlineStr"/>
@@ -5003,8 +5167,16 @@
       <c r="BH23" s="2" t="inlineStr"/>
       <c r="BI23" s="2" t="inlineStr"/>
       <c r="BJ23" s="2" t="inlineStr"/>
-      <c r="BK23" s="2" t="inlineStr"/>
-      <c r="BL23" s="2" t="inlineStr"/>
+      <c r="BK23" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5440,28 +5612,32 @@
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -5505,7 +5681,7 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -5514,7 +5690,11 @@
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr"/>
-      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>e9f028cb6f51459a95f823f89cb8f3c5</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
           <t>e55c0de93c8c282a799cc4c2</t>
@@ -5535,7 +5715,11 @@
       <c r="AL26" s="2" t="inlineStr"/>
       <c r="AM26" s="2" t="inlineStr"/>
       <c r="AN26" s="2" t="inlineStr"/>
-      <c r="AO26" s="2" t="inlineStr"/>
+      <c r="AO26" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP26" s="2" t="inlineStr"/>
       <c r="AQ26" s="2" t="inlineStr"/>
       <c r="AR26" s="2" t="inlineStr"/>
@@ -5571,10 +5755,22 @@
         </is>
       </c>
       <c r="BH26" s="2" t="inlineStr"/>
-      <c r="BI26" s="2" t="inlineStr"/>
+      <c r="BI26" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ26" s="2" t="inlineStr"/>
-      <c r="BK26" s="2" t="inlineStr"/>
-      <c r="BL26" s="2" t="inlineStr"/>
+      <c r="BK26" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -6025,13 +6221,17 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6084,7 +6284,11 @@
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr"/>
-      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>4583618979d546d68e0175d4b4907573</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
           <t>2eb5c0c469c50cd1c2a1609b</t>
@@ -6105,7 +6309,11 @@
       <c r="AL29" s="2" t="inlineStr"/>
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="inlineStr"/>
-      <c r="AO29" s="2" t="inlineStr"/>
+      <c r="AO29" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP29" s="2" t="inlineStr"/>
       <c r="AQ29" s="2" t="inlineStr"/>
       <c r="AR29" s="2" t="inlineStr"/>
@@ -6143,8 +6351,16 @@
       <c r="BH29" s="2" t="inlineStr"/>
       <c r="BI29" s="2" t="inlineStr"/>
       <c r="BJ29" s="2" t="inlineStr"/>
-      <c r="BK29" s="2" t="inlineStr"/>
-      <c r="BL29" s="2" t="inlineStr"/>
+      <c r="BK29" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6572,28 +6788,32 @@
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -6637,7 +6857,7 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -6646,7 +6866,11 @@
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr"/>
-      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>9e1b13250aed4ac5b4a155b6f4872c13</t>
+        </is>
+      </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
           <t>c677859ee3e109117dffbd40</t>
@@ -6667,7 +6891,11 @@
       <c r="AL32" s="2" t="inlineStr"/>
       <c r="AM32" s="2" t="inlineStr"/>
       <c r="AN32" s="2" t="inlineStr"/>
-      <c r="AO32" s="2" t="inlineStr"/>
+      <c r="AO32" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP32" s="2" t="inlineStr"/>
       <c r="AQ32" s="2" t="inlineStr"/>
       <c r="AR32" s="2" t="inlineStr"/>
@@ -6711,10 +6939,22 @@
         </is>
       </c>
       <c r="BH32" s="2" t="inlineStr"/>
-      <c r="BI32" s="2" t="inlineStr"/>
+      <c r="BI32" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ32" s="2" t="inlineStr"/>
-      <c r="BK32" s="2" t="inlineStr"/>
-      <c r="BL32" s="2" t="inlineStr"/>
+      <c r="BK32" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -7355,13 +7595,17 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -7414,7 +7658,11 @@
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr"/>
-      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>02bc8c432c4c4f22b166f93e159e1c7b</t>
+        </is>
+      </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
           <t>d130a1c9ad5e1f0665dd34fb</t>
@@ -7435,7 +7683,11 @@
       <c r="AL36" s="2" t="inlineStr"/>
       <c r="AM36" s="2" t="inlineStr"/>
       <c r="AN36" s="2" t="inlineStr"/>
-      <c r="AO36" s="2" t="inlineStr"/>
+      <c r="AO36" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP36" s="2" t="inlineStr"/>
       <c r="AQ36" s="2" t="inlineStr"/>
       <c r="AR36" s="2" t="inlineStr"/>
@@ -7481,8 +7733,16 @@
       <c r="BH36" s="2" t="inlineStr"/>
       <c r="BI36" s="2" t="inlineStr"/>
       <c r="BJ36" s="2" t="inlineStr"/>
-      <c r="BK36" s="2" t="inlineStr"/>
-      <c r="BL36" s="2" t="inlineStr"/>
+      <c r="BK36" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7720,28 +7980,32 @@
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -7785,7 +8049,7 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -7794,7 +8058,11 @@
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr"/>
-      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>76d354afbaeb4eecafe7c996581e5e49</t>
+        </is>
+      </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
           <t>01a70983277dbbb8d8f43fae</t>
@@ -7815,7 +8083,11 @@
       <c r="AL38" s="2" t="inlineStr"/>
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr"/>
-      <c r="AO38" s="2" t="inlineStr"/>
+      <c r="AO38" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP38" s="2" t="inlineStr"/>
       <c r="AQ38" s="2" t="inlineStr"/>
       <c r="AR38" s="2" t="inlineStr"/>
@@ -7851,10 +8123,22 @@
         </is>
       </c>
       <c r="BH38" s="2" t="inlineStr"/>
-      <c r="BI38" s="2" t="inlineStr"/>
+      <c r="BI38" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ38" s="2" t="inlineStr"/>
-      <c r="BK38" s="2" t="inlineStr"/>
-      <c r="BL38" s="2" t="inlineStr"/>
+      <c r="BK38" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -9466,28 +9750,32 @@
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -9531,7 +9819,7 @@
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -9540,7 +9828,11 @@
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr"/>
-      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>c49d127e885840a49e52bf3fb7908dbf</t>
+        </is>
+      </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
           <t>d2ca5c7e3c044dd8d67a5f1b</t>
@@ -9561,7 +9853,11 @@
       <c r="AL47" s="2" t="inlineStr"/>
       <c r="AM47" s="2" t="inlineStr"/>
       <c r="AN47" s="2" t="inlineStr"/>
-      <c r="AO47" s="2" t="inlineStr"/>
+      <c r="AO47" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP47" s="2" t="inlineStr"/>
       <c r="AQ47" s="2" t="inlineStr"/>
       <c r="AR47" s="2" t="inlineStr"/>
@@ -9597,10 +9893,22 @@
         </is>
       </c>
       <c r="BH47" s="2" t="inlineStr"/>
-      <c r="BI47" s="2" t="inlineStr"/>
+      <c r="BI47" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ47" s="2" t="inlineStr"/>
-      <c r="BK47" s="2" t="inlineStr"/>
-      <c r="BL47" s="2" t="inlineStr"/>
+      <c r="BK47" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -10055,13 +10363,17 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -10114,7 +10426,11 @@
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr"/>
-      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>43e66ec057fe4fcbabc07126b8d0d3f5</t>
+        </is>
+      </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
           <t>ef2067f09d80f9702ecbe6e6</t>
@@ -10135,7 +10451,11 @@
       <c r="AL50" s="2" t="inlineStr"/>
       <c r="AM50" s="2" t="inlineStr"/>
       <c r="AN50" s="2" t="inlineStr"/>
-      <c r="AO50" s="2" t="inlineStr"/>
+      <c r="AO50" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP50" s="2" t="inlineStr"/>
       <c r="AQ50" s="2" t="inlineStr"/>
       <c r="AR50" s="2" t="inlineStr"/>
@@ -10173,8 +10493,16 @@
       <c r="BH50" s="2" t="inlineStr"/>
       <c r="BI50" s="2" t="inlineStr"/>
       <c r="BJ50" s="2" t="inlineStr"/>
-      <c r="BK50" s="2" t="inlineStr"/>
-      <c r="BL50" s="2" t="inlineStr"/>
+      <c r="BK50" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -10225,13 +10553,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -10284,7 +10616,11 @@
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr"/>
-      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>37fe60c1919c4bb0ac9825c6f6715ee9</t>
+        </is>
+      </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
           <t>60703e3c0aa5ac337efa3ad3</t>
@@ -10305,7 +10641,11 @@
       <c r="AL51" s="2" t="inlineStr"/>
       <c r="AM51" s="2" t="inlineStr"/>
       <c r="AN51" s="2" t="inlineStr"/>
-      <c r="AO51" s="2" t="inlineStr"/>
+      <c r="AO51" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP51" s="2" t="inlineStr"/>
       <c r="AQ51" s="2" t="inlineStr"/>
       <c r="AR51" s="2" t="inlineStr"/>
@@ -10351,8 +10691,16 @@
       <c r="BH51" s="2" t="inlineStr"/>
       <c r="BI51" s="2" t="inlineStr"/>
       <c r="BJ51" s="2" t="inlineStr"/>
-      <c r="BK51" s="2" t="inlineStr"/>
-      <c r="BL51" s="2" t="inlineStr"/>
+      <c r="BK51" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -10403,13 +10751,17 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -10462,7 +10814,11 @@
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr"/>
-      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>d7602f6dffc64e029f8ab58c2efeef25</t>
+        </is>
+      </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
           <t>4d75f57501f2b2bcb19279e6</t>
@@ -10483,7 +10839,11 @@
       <c r="AL52" s="2" t="inlineStr"/>
       <c r="AM52" s="2" t="inlineStr"/>
       <c r="AN52" s="2" t="inlineStr"/>
-      <c r="AO52" s="2" t="inlineStr"/>
+      <c r="AO52" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP52" s="2" t="inlineStr"/>
       <c r="AQ52" s="2" t="inlineStr"/>
       <c r="AR52" s="2" t="inlineStr"/>
@@ -10529,8 +10889,16 @@
       <c r="BH52" s="2" t="inlineStr"/>
       <c r="BI52" s="2" t="inlineStr"/>
       <c r="BJ52" s="2" t="inlineStr"/>
-      <c r="BK52" s="2" t="inlineStr"/>
-      <c r="BL52" s="2" t="inlineStr"/>
+      <c r="BK52" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10768,28 +11136,32 @@
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -10833,7 +11205,7 @@
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -10842,7 +11214,11 @@
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr"/>
-      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>6c797653f6214088a11591b591ee20e4</t>
+        </is>
+      </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
           <t>b6e88deb800742bfa61d5f0c</t>
@@ -10863,7 +11239,11 @@
       <c r="AL54" s="2" t="inlineStr"/>
       <c r="AM54" s="2" t="inlineStr"/>
       <c r="AN54" s="2" t="inlineStr"/>
-      <c r="AO54" s="2" t="inlineStr"/>
+      <c r="AO54" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP54" s="2" t="inlineStr"/>
       <c r="AQ54" s="2" t="inlineStr"/>
       <c r="AR54" s="2" t="inlineStr"/>
@@ -10907,10 +11287,22 @@
         </is>
       </c>
       <c r="BH54" s="2" t="inlineStr"/>
-      <c r="BI54" s="2" t="inlineStr"/>
+      <c r="BI54" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ54" s="2" t="inlineStr"/>
-      <c r="BK54" s="2" t="inlineStr"/>
-      <c r="BL54" s="2" t="inlineStr"/>
+      <c r="BK54" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10946,28 +11338,32 @@
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -11011,7 +11407,7 @@
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -11020,7 +11416,11 @@
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr"/>
-      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>9783641f022240beb3ef83d37f71af3c</t>
+        </is>
+      </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
           <t>03e116cf47b64eacadd0f916</t>
@@ -11041,7 +11441,11 @@
       <c r="AL55" s="2" t="inlineStr"/>
       <c r="AM55" s="2" t="inlineStr"/>
       <c r="AN55" s="2" t="inlineStr"/>
-      <c r="AO55" s="2" t="inlineStr"/>
+      <c r="AO55" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP55" s="2" t="inlineStr"/>
       <c r="AQ55" s="2" t="inlineStr"/>
       <c r="AR55" s="2" t="inlineStr"/>
@@ -11077,10 +11481,22 @@
         </is>
       </c>
       <c r="BH55" s="2" t="inlineStr"/>
-      <c r="BI55" s="2" t="inlineStr"/>
+      <c r="BI55" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ55" s="2" t="inlineStr"/>
-      <c r="BK55" s="2" t="inlineStr"/>
-      <c r="BL55" s="2" t="inlineStr"/>
+      <c r="BK55" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -11116,28 +11532,32 @@
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -11181,7 +11601,7 @@
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -11190,7 +11610,11 @@
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr"/>
-      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>506ae8347a0e4883a0a6d2dcb004165b</t>
+        </is>
+      </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
           <t>31d7f2be91d905bf74c1b36a</t>
@@ -11211,7 +11635,11 @@
       <c r="AL56" s="2" t="inlineStr"/>
       <c r="AM56" s="2" t="inlineStr"/>
       <c r="AN56" s="2" t="inlineStr"/>
-      <c r="AO56" s="2" t="inlineStr"/>
+      <c r="AO56" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP56" s="2" t="inlineStr"/>
       <c r="AQ56" s="2" t="inlineStr"/>
       <c r="AR56" s="2" t="inlineStr"/>
@@ -11255,10 +11683,22 @@
         </is>
       </c>
       <c r="BH56" s="2" t="inlineStr"/>
-      <c r="BI56" s="2" t="inlineStr"/>
+      <c r="BI56" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ56" s="2" t="inlineStr"/>
-      <c r="BK56" s="2" t="inlineStr"/>
-      <c r="BL56" s="2" t="inlineStr"/>
+      <c r="BK56" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -11294,28 +11734,32 @@
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -11359,7 +11803,7 @@
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -11368,7 +11812,11 @@
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr"/>
-      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>d8ee206e033b400792c04508fd7116c5</t>
+        </is>
+      </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
           <t>058d4f93a7af09893629a9ee</t>
@@ -11389,7 +11837,11 @@
       <c r="AL57" s="2" t="inlineStr"/>
       <c r="AM57" s="2" t="inlineStr"/>
       <c r="AN57" s="2" t="inlineStr"/>
-      <c r="AO57" s="2" t="inlineStr"/>
+      <c r="AO57" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP57" s="2" t="inlineStr"/>
       <c r="AQ57" s="2" t="inlineStr"/>
       <c r="AR57" s="2" t="inlineStr"/>
@@ -11433,10 +11885,22 @@
         </is>
       </c>
       <c r="BH57" s="2" t="inlineStr"/>
-      <c r="BI57" s="2" t="inlineStr"/>
+      <c r="BI57" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ57" s="2" t="inlineStr"/>
-      <c r="BK57" s="2" t="inlineStr"/>
-      <c r="BL57" s="2" t="inlineStr"/>
+      <c r="BK57" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11472,28 +11936,32 @@
       <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -11537,7 +12005,7 @@
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -11546,7 +12014,11 @@
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr"/>
-      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>1f3b8e715d014c379ae8f8e2fd049367</t>
+        </is>
+      </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
           <t>b104a9a3c7d56563adec349d</t>
@@ -11567,7 +12039,11 @@
       <c r="AL58" s="2" t="inlineStr"/>
       <c r="AM58" s="2" t="inlineStr"/>
       <c r="AN58" s="2" t="inlineStr"/>
-      <c r="AO58" s="2" t="inlineStr"/>
+      <c r="AO58" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP58" s="2" t="inlineStr"/>
       <c r="AQ58" s="2" t="inlineStr"/>
       <c r="AR58" s="2" t="inlineStr"/>
@@ -11611,10 +12087,22 @@
         </is>
       </c>
       <c r="BH58" s="2" t="inlineStr"/>
-      <c r="BI58" s="2" t="inlineStr"/>
+      <c r="BI58" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ58" s="2" t="inlineStr"/>
-      <c r="BK58" s="2" t="inlineStr"/>
-      <c r="BL58" s="2" t="inlineStr"/>
+      <c r="BK58" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -12042,28 +12530,32 @@
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -12107,7 +12599,7 @@
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -12116,7 +12608,11 @@
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr"/>
-      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>40c43c65e4364b06b2512a308c32b9aa</t>
+        </is>
+      </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
           <t>394490f5a0143d59ff66454b</t>
@@ -12137,7 +12633,11 @@
       <c r="AL61" s="2" t="inlineStr"/>
       <c r="AM61" s="2" t="inlineStr"/>
       <c r="AN61" s="2" t="inlineStr"/>
-      <c r="AO61" s="2" t="inlineStr"/>
+      <c r="AO61" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP61" s="2" t="inlineStr"/>
       <c r="AQ61" s="2" t="inlineStr"/>
       <c r="AR61" s="2" t="inlineStr"/>
@@ -12181,10 +12681,22 @@
         </is>
       </c>
       <c r="BH61" s="2" t="inlineStr"/>
-      <c r="BI61" s="2" t="inlineStr"/>
+      <c r="BI61" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ61" s="2" t="inlineStr"/>
-      <c r="BK61" s="2" t="inlineStr"/>
-      <c r="BL61" s="2" t="inlineStr"/>
+      <c r="BK61" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL61" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -12220,28 +12732,32 @@
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -12285,7 +12801,7 @@
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -12294,7 +12810,11 @@
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr"/>
-      <c r="AB62" s="2" t="inlineStr"/>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>d9a35cc857a14ee1a5469ba6fa3cb3c3</t>
+        </is>
+      </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
           <t>1f6267d451e80b7b7be9377f</t>
@@ -12315,7 +12835,11 @@
       <c r="AL62" s="2" t="inlineStr"/>
       <c r="AM62" s="2" t="inlineStr"/>
       <c r="AN62" s="2" t="inlineStr"/>
-      <c r="AO62" s="2" t="inlineStr"/>
+      <c r="AO62" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP62" s="2" t="inlineStr"/>
       <c r="AQ62" s="2" t="inlineStr"/>
       <c r="AR62" s="2" t="inlineStr"/>
@@ -12351,10 +12875,22 @@
         </is>
       </c>
       <c r="BH62" s="2" t="inlineStr"/>
-      <c r="BI62" s="2" t="inlineStr"/>
+      <c r="BI62" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ62" s="2" t="inlineStr"/>
-      <c r="BK62" s="2" t="inlineStr"/>
-      <c r="BL62" s="2" t="inlineStr"/>
+      <c r="BK62" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL62" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -12595,13 +13131,17 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -12654,7 +13194,11 @@
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr"/>
-      <c r="AB64" s="2" t="inlineStr"/>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>214eddbf4bed497aa70200f61756bd89</t>
+        </is>
+      </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
           <t>84b282162797f63cc06f7269</t>
@@ -12675,7 +13219,11 @@
       <c r="AL64" s="2" t="inlineStr"/>
       <c r="AM64" s="2" t="inlineStr"/>
       <c r="AN64" s="2" t="inlineStr"/>
-      <c r="AO64" s="2" t="inlineStr"/>
+      <c r="AO64" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP64" s="2" t="inlineStr"/>
       <c r="AQ64" s="2" t="inlineStr"/>
       <c r="AR64" s="2" t="inlineStr"/>
@@ -12713,8 +13261,16 @@
       <c r="BH64" s="2" t="inlineStr"/>
       <c r="BI64" s="2" t="inlineStr"/>
       <c r="BJ64" s="2" t="inlineStr"/>
-      <c r="BK64" s="2" t="inlineStr"/>
-      <c r="BL64" s="2" t="inlineStr"/>
+      <c r="BK64" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -12948,28 +13504,32 @@
       <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -13013,7 +13573,7 @@
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -13022,7 +13582,11 @@
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr"/>
-      <c r="AB66" s="2" t="inlineStr"/>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>6eb2f90678ba407c87f43dcb6e959f5c</t>
+        </is>
+      </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
           <t>83dfdf2f8bf94b61150b4238</t>
@@ -13043,7 +13607,11 @@
       <c r="AL66" s="2" t="inlineStr"/>
       <c r="AM66" s="2" t="inlineStr"/>
       <c r="AN66" s="2" t="inlineStr"/>
-      <c r="AO66" s="2" t="inlineStr"/>
+      <c r="AO66" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP66" s="2" t="inlineStr"/>
       <c r="AQ66" s="2" t="inlineStr"/>
       <c r="AR66" s="2" t="inlineStr"/>
@@ -13087,10 +13655,22 @@
         </is>
       </c>
       <c r="BH66" s="2" t="inlineStr"/>
-      <c r="BI66" s="2" t="inlineStr"/>
+      <c r="BI66" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ66" s="2" t="inlineStr"/>
-      <c r="BK66" s="2" t="inlineStr"/>
-      <c r="BL66" s="2" t="inlineStr"/>
+      <c r="BK66" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL66" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -13331,13 +13911,17 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -13390,7 +13974,11 @@
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr"/>
-      <c r="AB68" s="2" t="inlineStr"/>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>005841bfb13241dcbfaf810c0d58c94b</t>
+        </is>
+      </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
           <t>893b3a732c45ad2e1838b1e4</t>
@@ -13411,7 +13999,11 @@
       <c r="AL68" s="2" t="inlineStr"/>
       <c r="AM68" s="2" t="inlineStr"/>
       <c r="AN68" s="2" t="inlineStr"/>
-      <c r="AO68" s="2" t="inlineStr"/>
+      <c r="AO68" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP68" s="2" t="inlineStr"/>
       <c r="AQ68" s="2" t="inlineStr"/>
       <c r="AR68" s="2" t="inlineStr"/>
@@ -13449,8 +14041,16 @@
       <c r="BH68" s="2" t="inlineStr"/>
       <c r="BI68" s="2" t="inlineStr"/>
       <c r="BJ68" s="2" t="inlineStr"/>
-      <c r="BK68" s="2" t="inlineStr"/>
-      <c r="BL68" s="2" t="inlineStr"/>
+      <c r="BK68" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL68" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -13901,13 +14501,17 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -13960,7 +14564,11 @@
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr"/>
-      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>b3320ac751064222ab3e4574950e2efb</t>
+        </is>
+      </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
           <t>f546deec9a73e6d2d58abd5b</t>
@@ -13981,7 +14589,11 @@
       <c r="AL71" s="2" t="inlineStr"/>
       <c r="AM71" s="2" t="inlineStr"/>
       <c r="AN71" s="2" t="inlineStr"/>
-      <c r="AO71" s="2" t="inlineStr"/>
+      <c r="AO71" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP71" s="2" t="inlineStr"/>
       <c r="AQ71" s="2" t="inlineStr"/>
       <c r="AR71" s="2" t="inlineStr"/>
@@ -14027,8 +14639,16 @@
       <c r="BH71" s="2" t="inlineStr"/>
       <c r="BI71" s="2" t="inlineStr"/>
       <c r="BJ71" s="2" t="inlineStr"/>
-      <c r="BK71" s="2" t="inlineStr"/>
-      <c r="BL71" s="2" t="inlineStr"/>
+      <c r="BK71" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL71" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -14064,28 +14684,32 @@
       <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -14129,7 +14753,7 @@
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
@@ -14138,7 +14762,11 @@
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr"/>
-      <c r="AB72" s="2" t="inlineStr"/>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>7178ae49df27487ba82f16de1b4faa13</t>
+        </is>
+      </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
           <t>9a497dfa896e5f1359135953</t>
@@ -14159,7 +14787,11 @@
       <c r="AL72" s="2" t="inlineStr"/>
       <c r="AM72" s="2" t="inlineStr"/>
       <c r="AN72" s="2" t="inlineStr"/>
-      <c r="AO72" s="2" t="inlineStr"/>
+      <c r="AO72" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP72" s="2" t="inlineStr"/>
       <c r="AQ72" s="2" t="inlineStr"/>
       <c r="AR72" s="2" t="inlineStr"/>
@@ -14195,10 +14827,22 @@
         </is>
       </c>
       <c r="BH72" s="2" t="inlineStr"/>
-      <c r="BI72" s="2" t="inlineStr"/>
+      <c r="BI72" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ72" s="2" t="inlineStr"/>
-      <c r="BK72" s="2" t="inlineStr"/>
-      <c r="BL72" s="2" t="inlineStr"/>
+      <c r="BK72" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL72" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -14249,13 +14893,17 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -14308,7 +14956,11 @@
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr"/>
-      <c r="AB73" s="2" t="inlineStr"/>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>42d4eed40a824d929a742c2b94133944</t>
+        </is>
+      </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
           <t>d11326693f407a55dceebb1f</t>
@@ -14329,7 +14981,11 @@
       <c r="AL73" s="2" t="inlineStr"/>
       <c r="AM73" s="2" t="inlineStr"/>
       <c r="AN73" s="2" t="inlineStr"/>
-      <c r="AO73" s="2" t="inlineStr"/>
+      <c r="AO73" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP73" s="2" t="inlineStr"/>
       <c r="AQ73" s="2" t="inlineStr"/>
       <c r="AR73" s="2" t="inlineStr"/>
@@ -14375,8 +15031,16 @@
       <c r="BH73" s="2" t="inlineStr"/>
       <c r="BI73" s="2" t="inlineStr"/>
       <c r="BJ73" s="2" t="inlineStr"/>
-      <c r="BK73" s="2" t="inlineStr"/>
-      <c r="BL73" s="2" t="inlineStr"/>
+      <c r="BK73" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL73" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -14831,13 +15495,17 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -14890,7 +15558,11 @@
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr"/>
-      <c r="AB76" s="2" t="inlineStr"/>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>95accf2ecef14bdfb1631640a5ad6ca8</t>
+        </is>
+      </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
           <t>69c73ced5c749585e1ab6878</t>
@@ -14911,7 +15583,11 @@
       <c r="AL76" s="2" t="inlineStr"/>
       <c r="AM76" s="2" t="inlineStr"/>
       <c r="AN76" s="2" t="inlineStr"/>
-      <c r="AO76" s="2" t="inlineStr"/>
+      <c r="AO76" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP76" s="2" t="inlineStr"/>
       <c r="AQ76" s="2" t="inlineStr"/>
       <c r="AR76" s="2" t="inlineStr"/>
@@ -14949,8 +15625,16 @@
       <c r="BH76" s="2" t="inlineStr"/>
       <c r="BI76" s="2" t="inlineStr"/>
       <c r="BJ76" s="2" t="inlineStr"/>
-      <c r="BK76" s="2" t="inlineStr"/>
-      <c r="BL76" s="2" t="inlineStr"/>
+      <c r="BK76" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL76" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14986,28 +15670,32 @@
       <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -15051,7 +15739,7 @@
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -15060,7 +15748,11 @@
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr"/>
-      <c r="AB77" s="2" t="inlineStr"/>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>029f36e7c6d342c8a1516d6d3272a603</t>
+        </is>
+      </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
           <t>629aff4e78c2a88cee56fafa</t>
@@ -15081,7 +15773,11 @@
       <c r="AL77" s="2" t="inlineStr"/>
       <c r="AM77" s="2" t="inlineStr"/>
       <c r="AN77" s="2" t="inlineStr"/>
-      <c r="AO77" s="2" t="inlineStr"/>
+      <c r="AO77" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP77" s="2" t="inlineStr"/>
       <c r="AQ77" s="2" t="inlineStr"/>
       <c r="AR77" s="2" t="inlineStr"/>
@@ -15117,10 +15813,22 @@
         </is>
       </c>
       <c r="BH77" s="2" t="inlineStr"/>
-      <c r="BI77" s="2" t="inlineStr"/>
+      <c r="BI77" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ77" s="2" t="inlineStr"/>
-      <c r="BK77" s="2" t="inlineStr"/>
-      <c r="BL77" s="2" t="inlineStr"/>
+      <c r="BK77" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL77" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -15171,13 +15879,17 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -15230,7 +15942,11 @@
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr"/>
-      <c r="AB78" s="2" t="inlineStr"/>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>86f32cf533a74ad99d3488aa5ca2dcf9</t>
+        </is>
+      </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
           <t>b34366f7cd129e694bac1ac9</t>
@@ -15251,7 +15967,11 @@
       <c r="AL78" s="2" t="inlineStr"/>
       <c r="AM78" s="2" t="inlineStr"/>
       <c r="AN78" s="2" t="inlineStr"/>
-      <c r="AO78" s="2" t="inlineStr"/>
+      <c r="AO78" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP78" s="2" t="inlineStr"/>
       <c r="AQ78" s="2" t="inlineStr"/>
       <c r="AR78" s="2" t="inlineStr"/>
@@ -15289,8 +16009,16 @@
       <c r="BH78" s="2" t="inlineStr"/>
       <c r="BI78" s="2" t="inlineStr"/>
       <c r="BJ78" s="2" t="inlineStr"/>
-      <c r="BK78" s="2" t="inlineStr"/>
-      <c r="BL78" s="2" t="inlineStr"/>
+      <c r="BK78" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL78" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:BL78"/>
